--- a/Shared/XLS/Buff.xlsx
+++ b/Shared/XLS/Buff.xlsx
@@ -4,170 +4,174 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
-    <sheet name="#Buff" sheetId="4" r:id="rId2"/>
+    <sheet name="#Buff" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="50">
+  <si>
+    <t>!Enum</t>
+  </si>
+  <si>
+    <t>BuffStackPolicy</t>
+  </si>
+  <si>
+    <t>Refresh</t>
+  </si>
+  <si>
+    <t>지속시간만 갱신(둔화, 기절, 스탯 버프)</t>
+  </si>
+  <si>
+    <t>Independent</t>
+  </si>
+  <si>
+    <t>스택마다 독립 인스턴스(화상, 출혈)</t>
+  </si>
+  <si>
+    <t>Extend</t>
+  </si>
+  <si>
+    <t>남은 시간에 가산(보호막)</t>
+  </si>
+  <si>
+    <t>Ignore</t>
+  </si>
+  <si>
+    <t>이미 있으면 무시(고유 각인)</t>
+  </si>
+  <si>
+    <t>ActionBlockType</t>
+  </si>
+  <si>
+    <t>Move</t>
+  </si>
+  <si>
+    <t>이동 불가</t>
+  </si>
+  <si>
+    <t>Turn</t>
+  </si>
+  <si>
+    <t>회전 불가</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>일반 공격 불가</t>
+  </si>
+  <si>
+    <t>Cast</t>
+  </si>
+  <si>
+    <t>스킬 시전 불가. 진행 중인 시전도 취소</t>
+  </si>
   <si>
     <t>!EnumTable</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Buff</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Desc</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Icon</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>IsDebuff</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>StackPolicy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>TickInterval</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>BlockFlags</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>EffectID_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>EffectID_02</t>
   </si>
   <si>
     <t>!Buff</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>!bool</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>!BuffStackPolicy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!ActionBlockType</t>
   </si>
   <si>
     <t>!SkillEffect</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Move</t>
-  </si>
-  <si>
-    <t>Cast</t>
-  </si>
-  <si>
-    <t>!Enum</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffStackPolicy</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Refresh</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>지속시간만 갱신(둔화, 기절, 스탯 버프)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Independent</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>스택마다 독립 인스턴스(화상, 출혈)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Extend</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>남은 시간에 가산(보호막)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ignore</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이미 있으면 무시(고유 각인)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActionBlockType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동 불가</t>
-  </si>
-  <si>
-    <t>Attack</t>
-  </si>
-  <si>
-    <t>일반 공격 불가</t>
-  </si>
-  <si>
-    <t>!ActionBlockType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>스킬 시전 불가. 진행 중인 시전도 취소</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>회전 불가</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Turn</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_Stagger</t>
+  </si>
+  <si>
+    <t>경직</t>
+  </si>
+  <si>
+    <t>피격 경직 - 이동/공격/스킬 시전 불가</t>
+  </si>
+  <si>
+    <t>Move;Attack;Cast</t>
+  </si>
+  <si>
+    <t>BUFF_Stun</t>
+  </si>
+  <si>
+    <t>기절</t>
+  </si>
+  <si>
+    <t>기절 - 이동/회전/공격/스킬 시전 불가</t>
+  </si>
+  <si>
+    <t>Move;Turn;Attack;Cast</t>
+  </si>
+  <si>
+    <t>BUFF_DamageTakenUp</t>
+  </si>
+  <si>
+    <t>취약</t>
+  </si>
+  <si>
+    <t>받는 피해 증가</t>
+  </si>
+  <si>
+    <t>SE_Debuff_DamageTakenUp_StatChange</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,13 +191,6 @@
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -359,15 +356,15 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -381,36 +378,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -685,7 +678,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -696,289 +689,284 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.25" style="4" customWidth="1"/>
-    <col min="3" max="3" width="36.75" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.5" style="9" customWidth="1"/>
-    <col min="5" max="5" width="150.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="4"/>
+    <col min="3" max="3" width="36.75" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.5" style="8" customWidth="1"/>
+    <col min="5" max="5" width="150.25" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="14" customFormat="1">
-      <c r="A1" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="11"/>
+    <row r="1" spans="1:5" s="12" customFormat="1">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="B2" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>23</v>
+      <c r="B2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="B3" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>25</v>
+      <c r="B3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="B4" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>27</v>
+      <c r="B4" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="B5" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>29</v>
+      <c r="B5" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="B6" s="5"/>
-    </row>
-    <row r="7" spans="1:5" s="14" customFormat="1">
-      <c r="A7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="11"/>
+      <c r="B6" s="14"/>
+    </row>
+    <row r="7" spans="1:5" s="12" customFormat="1">
+      <c r="A7" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="10"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="B9" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="B10" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
         <v>18</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="B9" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="B10" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="B11" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="14.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.75" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.75" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.875" style="5" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="4"/>
+    <col min="2" max="2" width="22.5" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.375" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.75" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.125" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.625" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5" style="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.25" style="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.75" style="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="39.125" style="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.875" style="14" customWidth="1"/>
+    <col min="12" max="12" width="9" style="4" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="2" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="B2" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="B3" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="I4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" t="b">
         <v>1</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="B2" s="5" t="s">
+      <c r="G5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="B3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="J6" t="s">
+        <v>49</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Shared/XLS/Buff.xlsx
+++ b/Shared/XLS/Buff.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
   <si>
     <t>!Enum</t>
   </si>
@@ -165,6 +165,26 @@
   </si>
   <si>
     <t>SE_Debuff_DamageTakenUp_StatChange</t>
+  </si>
+  <si>
+    <t>Independent</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_BuffRune_AtkUp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_CombatRune</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전투 보조 룬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_BuffRune_DefUp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -678,7 +698,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -796,7 +816,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -964,6 +984,26 @@
         <v>49</v>
       </c>
     </row>
+    <row r="7" spans="1:11">
+      <c r="B7" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="14">
+        <v>0</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Shared/XLS/Buff.xlsx
+++ b/Shared/XLS/Buff.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="63">
   <si>
     <t>!Enum</t>
   </si>
@@ -104,86 +104,112 @@
     <t>BlockFlags</t>
   </si>
   <si>
+    <t>IgnoreImmune</t>
+  </si>
+  <si>
+    <t>DebuffMotion</t>
+  </si>
+  <si>
+    <t>EffectID_02</t>
+  </si>
+  <si>
+    <t>!Buff</t>
+  </si>
+  <si>
+    <t>!string</t>
+  </si>
+  <si>
+    <t>!bool</t>
+  </si>
+  <si>
+    <t>!BuffStackPolicy</t>
+  </si>
+  <si>
+    <t>!float</t>
+  </si>
+  <si>
+    <t>!ActionBlockType</t>
+  </si>
+  <si>
+    <t>!SkillEffect</t>
+  </si>
+  <si>
+    <t>BUFF_Stagger</t>
+  </si>
+  <si>
+    <t>경직</t>
+  </si>
+  <si>
+    <t>피격 경직 - 이동/공격/스킬 시전 불가</t>
+  </si>
+  <si>
+    <t>Move;Attack;Cast</t>
+  </si>
+  <si>
+    <t>BUFF_Stun</t>
+  </si>
+  <si>
+    <t>기절</t>
+  </si>
+  <si>
+    <t>기절 - 이동/회전/공격/스킬 시전 불가</t>
+  </si>
+  <si>
+    <t>Move;Turn;Attack;Cast</t>
+  </si>
+  <si>
+    <t>취약</t>
+  </si>
+  <si>
+    <t>받는 피해 증가</t>
+  </si>
+  <si>
+    <t>SE_Debuff_DamageTakenUp_StatChange</t>
+  </si>
+  <si>
+    <t>BUFF_CombatRune</t>
+  </si>
+  <si>
+    <t>전투 보조 룬</t>
+  </si>
+  <si>
+    <t>SE_BuffRune_AtkUp</t>
+  </si>
+  <si>
+    <t>SE_BuffRune_DefUp</t>
+  </si>
+  <si>
+    <t>무적</t>
+  </si>
+  <si>
+    <t>받는 피해 무효</t>
+  </si>
+  <si>
+    <t>BUFF_DamageTakenUp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 기절</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기절! 받는 데미지 +100%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_Invincible</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>EffectID_01</t>
-  </si>
-  <si>
-    <t>EffectID_02</t>
-  </si>
-  <si>
-    <t>!Buff</t>
-  </si>
-  <si>
-    <t>!string</t>
-  </si>
-  <si>
-    <t>!bool</t>
-  </si>
-  <si>
-    <t>!BuffStackPolicy</t>
-  </si>
-  <si>
-    <t>!float</t>
-  </si>
-  <si>
-    <t>!ActionBlockType</t>
-  </si>
-  <si>
-    <t>!SkillEffect</t>
-  </si>
-  <si>
-    <t>BUFF_Stagger</t>
-  </si>
-  <si>
-    <t>경직</t>
-  </si>
-  <si>
-    <t>피격 경직 - 이동/공격/스킬 시전 불가</t>
-  </si>
-  <si>
-    <t>Move;Attack;Cast</t>
-  </si>
-  <si>
-    <t>BUFF_Stun</t>
-  </si>
-  <si>
-    <t>기절</t>
-  </si>
-  <si>
-    <t>기절 - 이동/회전/공격/스킬 시전 불가</t>
-  </si>
-  <si>
-    <t>Move;Turn;Attack;Cast</t>
-  </si>
-  <si>
-    <t>BUFF_DamageTakenUp</t>
-  </si>
-  <si>
-    <t>취약</t>
-  </si>
-  <si>
-    <t>받는 피해 증가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>SE_Debuff_DamageTakenUp_StatChange</t>
-  </si>
-  <si>
-    <t>Independent</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>SE_BuffRune_AtkUp</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_CombatRune</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>전투 보조 룬</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_BuffRune_DefUp</t>
+    <t>BUFF_BreakStun</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -714,8 +740,8 @@
     <col min="3" max="3" width="36.75" style="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="2.5" style="8" customWidth="1"/>
     <col min="5" max="5" width="150.25" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="4" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="4"/>
+    <col min="6" max="8" width="9" style="4" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="12" customFormat="1">
@@ -816,7 +842,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -827,14 +853,15 @@
     <col min="6" max="6" width="8.625" style="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.5" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.25" style="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.75" style="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="39.125" style="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.875" style="14" customWidth="1"/>
-    <col min="12" max="12" width="9" style="4" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="4"/>
+    <col min="9" max="9" width="21.375" style="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.375" style="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="39.125" style="14" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="39.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="9" style="4" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" ht="18" customHeight="1">
+    <row r="1" spans="1:13" s="2" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -848,10 +875,10 @@
       <c r="G1" s="11"/>
       <c r="H1" s="11"/>
       <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+    </row>
+    <row r="2" spans="1:13">
       <c r="B2" s="14" t="s">
         <v>21</v>
       </c>
@@ -876,54 +903,66 @@
       <c r="I2" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="B3" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G3" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="K3" s="14" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="K3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="B4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -935,18 +974,18 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="B5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -958,12 +997,15 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>46</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="B6" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
         <v>47</v>
@@ -980,28 +1022,77 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="J6" t="s">
+      <c r="L6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:13">
       <c r="B7" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="H7" s="14">
         <v>0</v>
       </c>
-      <c r="J7" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="K7" s="14" t="s">
+      <c r="L7" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="B8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" t="s">
         <v>54</v>
+      </c>
+      <c r="D8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" t="s">
+        <v>2</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="B9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
